--- a/students-courses/share/documents/courses/reports/courses-by-department.xlsx
+++ b/students-courses/share/documents/courses/reports/courses-by-department.xlsx
@@ -7,9 +7,9 @@
     <sheet sheetId="1" name="Courses by department" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Courses by department'!$B1:$L22</definedName>
     <definedName name="CourseDepartmentNames">OFFSET('Courses by department'!$B$4,0,0,COUNT('Courses by department'!$C$4:$C$103),1)</definedName>
     <definedName name="CourseDepartmentCounts">OFFSET('Courses by department'!$C$4,0,0,COUNT('Courses by department'!$C$4:$C$103),1)</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Courses by department'!$B1:$L22</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
@@ -42,14 +42,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="4">
     <font>
-      <color theme="1"/>
-      <family val="2"/>
-      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -107,21 +105,11 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -550,22 +538,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L103"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <cols>
-    <col min="1" max="1" width="9" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="9" customWidth="1" hidden="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="9" hidden="1" customWidth="1"/>
-    <col min="5" max="12" width="12" customWidth="1"/>
+    <col min="4" max="4" width="9" customWidth="1" hidden="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
+    <row r="1" ht="30" customHeight="1">
+      <c r="B1" t="s" s="1">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
@@ -579,421 +569,421 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
+    <row r="3">
+      <c r="B3" t="s" s="2">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s" s="3">
         <v>4</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" t="s" s="4">
         <v>5</v>
       </c>
       <c r="D4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="35">
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="36">
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
     </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
     </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
     </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="45">
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
     </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="46">
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
     </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="47">
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
     </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="48">
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="49">
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="50">
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="51">
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="52">
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="53">
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="54">
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="55">
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="56">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="57">
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
     </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="58">
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
     </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="59">
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
     </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="60">
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="61">
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="62">
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
     </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="63">
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
     </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="64">
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
     </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="65">
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
     </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="66">
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="67">
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
     </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="68">
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
     </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="69">
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="70">
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
     </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="71">
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
     </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="72">
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
     </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="73">
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
     </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="74">
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
     </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="75">
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
     </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="76">
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
     </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="77">
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
     </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="78">
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
     </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="79">
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
     </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="80">
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
     </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="81">
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
     </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="82">
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
     </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="83">
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
     </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="84">
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
     </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="85">
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
     </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="86">
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
     </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="87">
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
     </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="88">
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
     </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="89">
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
     </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="90">
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
     </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="91">
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
     </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="92">
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
     </row>
-    <row r="93" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="93">
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
     </row>
-    <row r="94" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="94">
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
     </row>
-    <row r="95" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="95">
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
     </row>
-    <row r="96" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="96">
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
     </row>
-    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="97">
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
     </row>
-    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="98">
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
     </row>
-    <row r="99" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="99">
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
     </row>
-    <row r="100" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="100">
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
     </row>
-    <row r="101" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="101">
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
     </row>
-    <row r="102" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="102">
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
     </row>
-    <row r="103" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="103">
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
     </row>
@@ -1001,8 +991,7 @@
   <mergeCells count="1">
     <mergeCell ref="B1:L1"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="1" scale="100" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>